--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,45 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>438681</v>
+        <v>137091434</v>
       </c>
       <c r="B2" t="n">
-        <v>75390</v>
+        <v>75479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1458</v>
+        <v>1114</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sjuhalla gård, Bl</t>
+          <t>Sjuhalla, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534499</v>
+        <v>534461</v>
       </c>
       <c r="R2" t="n">
-        <v>6227924</v>
+        <v>6227987</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-09-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-09-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Inventering av skyddsvärda träd (ÅGP)</t>
+          <t>Rikligt i form av "blyertslav" på senvuxen ek.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,42 +767,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Joakim Andersson Hemberg, Ola Runfors, Madeleine Franzon</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/438681</t>
+          <t>https://artportalen.se/Sighting/137091434</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>741599</v>
+        <v>438681</v>
       </c>
       <c r="B3" t="n">
-        <v>96231</v>
+        <v>75390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>1458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534444</v>
+        <v>534499</v>
       </c>
       <c r="R3" t="n">
-        <v>6227973</v>
+        <v>6227924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2008-08-22</t>
+          <t>2008-09-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2008-08-22</t>
+          <t>2008-09-08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -906,16 +901,16 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/741599</t>
+          <t>https://artportalen.se/Sighting/438681</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1562911</v>
+        <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>91867</v>
+        <v>92950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,34 +918,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5445</v>
+        <v>2014</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sjuhalla gård, Bl</t>
+          <t>Sjuhalla, Bl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534463</v>
+        <v>534452</v>
       </c>
       <c r="R4" t="n">
-        <v>6228020</v>
+        <v>6228006</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,17 +983,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2008-08-22</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2008-08-22</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Inventering av skyddsvärda träd (ÅGP)</t>
+          <t>Ett tiotal fruktkroppar på grov boklåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,77 +1002,80 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Joakim Andersson Hemberg, Ola Runfors, Madeleine Franzon</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1562911</t>
+          <t>https://artportalen.se/Sighting/137091322</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1871182</v>
+        <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>75300</v>
+        <v>92950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>2014</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sjuhalla gård, Bl</t>
+          <t>Sjuhalla, Bl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534558</v>
+        <v>534579</v>
       </c>
       <c r="R5" t="n">
-        <v>6227921</v>
+        <v>6228018</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,17 +1102,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2008-09-11</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2008-09-11</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Inventering av skyddsvärda träd (ÅGP)</t>
+          <t>En liten fruktkropp på boklåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,42 +1121,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Joakim Andersson Hemberg, Ola Runfors, Madeleine Franzon</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1871182</t>
+          <t>https://artportalen.se/Sighting/137091650</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2107106</v>
+        <v>741599</v>
       </c>
       <c r="B6" t="n">
-        <v>79707</v>
+        <v>96231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1156,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6431</v>
+        <v>2779</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1254,16 +1255,16 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2107106</t>
+          <t>https://artportalen.se/Sighting/741599</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2442400</v>
+        <v>137091905</v>
       </c>
       <c r="B7" t="n">
-        <v>78728</v>
+        <v>90012</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,37 +1272,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6436</v>
+        <v>2979</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Lömsk flugsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Amanita phalloides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Fr.:Fr.) Link</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sjuhalla gård, Bl</t>
+          <t>Sjuhalla, Bl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534434</v>
+        <v>534544</v>
       </c>
       <c r="R7" t="n">
-        <v>6227978</v>
+        <v>6228108</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,17 +1329,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2008-08-22</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2008-08-22</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Inventering av skyddsvärda träd (ÅGP)</t>
+          <t>Spridda fruktkroppar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,93 +1348,69 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Joakim Andersson Hemberg, Ola Runfors, Madeleine Franzon</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2442400</t>
+          <t>https://artportalen.se/Sighting/137091905</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>76584005</v>
+        <v>1562911</v>
       </c>
       <c r="B8" t="n">
-        <v>57890</v>
+        <v>91867</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100082</v>
+        <v>5445</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sjuhalla gård, torpet, Bl</t>
+          <t>Sjuhalla gård, Bl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534561</v>
+        <v>534463</v>
       </c>
       <c r="R8" t="n">
-        <v>6227822</v>
+        <v>6228020</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,12 +1437,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-03-25</t>
+          <t>2008-08-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-03-25</t>
+          <t>2008-08-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd (ÅGP)</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,31 +1458,40 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sanne Svensson</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sanne Svensson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/76584005</t>
+          <t>https://artportalen.se/Sighting/1562911</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7871</v>
+        <v>1871182</v>
       </c>
       <c r="B9" t="n">
-        <v>58816</v>
+        <v>75300</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,43 +1499,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100117</v>
+        <v>6428</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana dalmatina</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bonaparte, 1840</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>ägg</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>60 Sjuhalla, Bl</t>
+          <t>Sjuhalla gård, Bl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534514</v>
+        <v>534558</v>
       </c>
       <c r="R9" t="n">
-        <v>6227841</v>
+        <v>6227921</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,17 +1553,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2007-03-28</t>
+          <t>2008-09-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2007-03-28</t>
+          <t>2008-09-11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Kärr i lövskog, ca 15x50m stort.En kraftledningsgata går väster om vattnet, och en gård ligger nordost om det.</t>
+          <t>Inventering av skyddsvärda träd (ÅGP)</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,31 +1574,40 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Blekinge (Anly)</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Annika Lydänge</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7871</t>
+          <t>https://artportalen.se/Sighting/1871182</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>76559629</v>
+        <v>2107106</v>
       </c>
       <c r="B10" t="n">
-        <v>9403</v>
+        <v>79707</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,43 +1615,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100859</v>
+        <v>6431</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bokoxe</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dorcus parallelipipedus</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sjuhalla gård, torpet, Bl</t>
+          <t>Sjuhalla gård, Bl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534561</v>
+        <v>534444</v>
       </c>
       <c r="R10" t="n">
-        <v>6227822</v>
+        <v>6227973</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,12 +1669,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2008-08-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2008-08-22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd (ÅGP)</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,34 +1688,42 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sanne Svensson</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sanne Svensson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/76559629</t>
+          <t>https://artportalen.se/Sighting/2107106</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>76585400</v>
+        <v>2442400</v>
       </c>
       <c r="B11" t="n">
-        <v>57947</v>
+        <v>78728</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,46 +1731,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102977</v>
+        <v>6436</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sjuhalla gård, torpet, Bl</t>
+          <t>Sjuhalla gård, Bl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534561</v>
+        <v>534434</v>
       </c>
       <c r="R11" t="n">
-        <v>6227822</v>
+        <v>6227978</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,12 +1785,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2008-08-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2008-08-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd (ÅGP)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,48 +1806,57 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sanne Svensson</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sanne Svensson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/76585400</t>
+          <t>https://artportalen.se/Sighting/2442400</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>76554802</v>
+        <v>76584005</v>
       </c>
       <c r="B12" t="n">
-        <v>58497</v>
+        <v>57890</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102990</v>
+        <v>100082</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1877,7 +1877,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1917,12 +1917,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-03-24</t>
+          <t>2019-03-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-03-24</t>
+          <t>2019-03-25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,67 +1948,60 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/76554802</t>
+          <t>https://artportalen.se/Sighting/76584005</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>76584129</v>
+        <v>7871</v>
       </c>
       <c r="B13" t="n">
-        <v>58112</v>
+        <v>58816</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103020</v>
+        <v>100117</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rana dalmatina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Bonaparte, 1840</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>ägg</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sjuhalla gård, torpet, Bl</t>
+          <t>60 Sjuhalla, Bl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534561</v>
+        <v>534514</v>
       </c>
       <c r="R13" t="n">
-        <v>6227822</v>
+        <v>6227841</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2035,12 +2028,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-03-25</t>
+          <t>2007-03-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-03-25</t>
+          <t>2007-03-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kärr i lövskog, ca 15x50m stort.En kraftledningsgata går väster om vattnet, och en gård ligger nordost om det.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,64 +2053,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sanne Svensson</t>
+          <t>Länsstyrelsen i Blekinge (Anly)</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sanne Svensson</t>
+          <t>Annika Lydänge</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/76584129</t>
+          <t>https://artportalen.se/Sighting/7871</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>76584318</v>
+        <v>76559629</v>
       </c>
       <c r="B14" t="n">
-        <v>58676</v>
+        <v>9403</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103055</v>
+        <v>100859</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Bokoxe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dorcus parallelipipedus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2150,12 +2144,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2019-03-25</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2019-03-25</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,16 +2176,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/76584318</t>
+          <t>https://artportalen.se/Sighting/76559629</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>76584304</v>
+        <v>76585400</v>
       </c>
       <c r="B15" t="n">
-        <v>58085</v>
+        <v>57947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,16 +2193,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205976</v>
+        <v>102977</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2221,7 +2215,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
@@ -2266,12 +2259,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2019-03-25</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2019-03-25</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,7 +2273,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2298,55 +2290,67 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/76584304</t>
+          <t>https://artportalen.se/Sighting/76585400</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>83599864</v>
+        <v>76554802</v>
       </c>
       <c r="B16" t="n">
-        <v>106813</v>
+        <v>58497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220785</v>
+        <v>102990</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ask (Skyddsvärt träd), Bl</t>
+          <t>Sjuhalla gård, torpet, Bl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534444</v>
+        <v>534561</v>
       </c>
       <c r="R16" t="n">
-        <v>6227973</v>
+        <v>6227822</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,19 +2375,14 @@
           <t>Nättraby</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>22B9722F-6811-4EF9-9F15-EB8D657D1297</t>
-        </is>
-      </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2008-08-22</t>
+          <t>2019-03-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2008-08-22</t>
+          <t>2019-03-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,70 +2397,78 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Karlsson</t>
+          <t>Sanne Svensson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Karlsson, Mattias Lif</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Sanne Svensson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83599864</t>
+          <t>https://artportalen.se/Sighting/76554802</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>83601655</v>
+        <v>76584129</v>
       </c>
       <c r="B17" t="n">
-        <v>106813</v>
+        <v>58112</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220785</v>
+        <v>103020</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ask (Skyddsvärt träd), Bl</t>
+          <t>Sjuhalla gård, torpet, Bl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534441</v>
+        <v>534561</v>
       </c>
       <c r="R17" t="n">
-        <v>6228118</v>
+        <v>6227822</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2486,19 +2493,14 @@
           <t>Nättraby</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>2D025A3F-0F87-4CC1-B3DE-29B5DC381D94</t>
-        </is>
-      </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2008-08-22</t>
+          <t>2019-03-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2008-08-22</t>
+          <t>2019-03-25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,70 +2515,75 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Karlsson</t>
+          <t>Sanne Svensson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Karlsson, Mattias Lif</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Sanne Svensson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83601655</t>
+          <t>https://artportalen.se/Sighting/76584129</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>83601664</v>
+        <v>76584318</v>
       </c>
       <c r="B18" t="n">
-        <v>106813</v>
+        <v>58676</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220785</v>
+        <v>103055</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ask (Skyddsvärt träd), Bl</t>
+          <t>Sjuhalla gård, torpet, Bl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534467</v>
+        <v>534561</v>
       </c>
       <c r="R18" t="n">
-        <v>6227912</v>
+        <v>6227822</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2601,19 +2608,14 @@
           <t>Nättraby</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>16460B8F-7657-424F-96A1-89E5C316E70C</t>
-        </is>
-      </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2008-08-22</t>
+          <t>2019-03-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2008-08-22</t>
+          <t>2019-03-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2622,76 +2624,82 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Karlsson</t>
+          <t>Sanne Svensson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Karlsson, Mattias Lif</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Sanne Svensson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83601664</t>
+          <t>https://artportalen.se/Sighting/76584318</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>83605926</v>
+        <v>76584304</v>
       </c>
       <c r="B19" t="n">
-        <v>106813</v>
+        <v>58085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220785</v>
+        <v>205976</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ask (Skyddsvärt träd), Bl</t>
+          <t>Sjuhalla gård, torpet, Bl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534440</v>
+        <v>534561</v>
       </c>
       <c r="R19" t="n">
-        <v>6227911</v>
+        <v>6227822</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2716,19 +2724,14 @@
           <t>Nättraby</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9EB987EB-9A2D-48CE-990A-400D11003DDF</t>
-        </is>
-      </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2008-10-08</t>
+          <t>2019-03-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2008-10-08</t>
+          <t>2019-03-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2737,26 +2740,483 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
+          <t>Sanne Svensson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sanne Svensson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76584304</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>83599864</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Bl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>534444</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6227973</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nättraby</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>22B9722F-6811-4EF9-9F15-EB8D657D1297</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2008-08-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2008-08-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Johan Karlsson</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Johan Karlsson, Mattias Lif</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
+      <c r="AY20" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83599864</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>83601655</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Bl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>534441</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6228118</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nättraby</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2D025A3F-0F87-4CC1-B3DE-29B5DC381D94</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2008-08-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2008-08-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Johan Karlsson, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83601655</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>83601664</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Bl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>534467</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6227912</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nättraby</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>16460B8F-7657-424F-96A1-89E5C316E70C</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2008-08-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2008-08-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Johan Karlsson, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83601664</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>83605926</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Bl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>534440</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6227911</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nättraby</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>9EB987EB-9A2D-48CE-990A-400D11003DDF</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2008-10-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2008-10-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Johan Karlsson, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/83605926</t>
         </is>
@@ -2782,6 +3242,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>92950</v>
+        <v>92951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>92950</v>
+        <v>92951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137091905</v>
       </c>
       <c r="B7" t="n">
-        <v>90012</v>
+        <v>90013</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>92951</v>
+        <v>92957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>92951</v>
+        <v>92957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137091905</v>
       </c>
       <c r="B7" t="n">
-        <v>90013</v>
+        <v>90019</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>92957</v>
+        <v>92961</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>92957</v>
+        <v>92961</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137091905</v>
       </c>
       <c r="B7" t="n">
-        <v>90019</v>
+        <v>90023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>92961</v>
+        <v>92963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>92961</v>
+        <v>92963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137091905</v>
       </c>
       <c r="B7" t="n">
-        <v>90023</v>
+        <v>90025</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091434</v>
       </c>
       <c r="B2" t="n">
-        <v>75479</v>
+        <v>75492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>92963</v>
+        <v>92976</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>92963</v>
+        <v>92976</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137091905</v>
       </c>
       <c r="B7" t="n">
-        <v>90025</v>
+        <v>90038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091434</v>
       </c>
       <c r="B2" t="n">
-        <v>75492</v>
+        <v>75494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>92976</v>
+        <v>92978</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>92976</v>
+        <v>92978</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137091905</v>
       </c>
       <c r="B7" t="n">
-        <v>90038</v>
+        <v>90040</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>92978</v>
+        <v>92981</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>92978</v>
+        <v>92981</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137091905</v>
       </c>
       <c r="B7" t="n">
-        <v>90040</v>
+        <v>90043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091434</v>
       </c>
       <c r="B2" t="n">
-        <v>75494</v>
+        <v>75504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>92981</v>
+        <v>92991</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>92981</v>
+        <v>92991</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137091905</v>
       </c>
       <c r="B7" t="n">
-        <v>90043</v>
+        <v>90053</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>92991</v>
+        <v>92992</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>92991</v>
+        <v>92992</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137091905</v>
       </c>
       <c r="B7" t="n">
-        <v>90053</v>
+        <v>90054</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091434</v>
       </c>
       <c r="B2" t="n">
-        <v>75504</v>
+        <v>75507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>92992</v>
+        <v>92995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>92992</v>
+        <v>92995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137091905</v>
       </c>
       <c r="B7" t="n">
-        <v>90054</v>
+        <v>90057</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>92995</v>
+        <v>92997</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>92995</v>
+        <v>92997</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091434</v>
       </c>
       <c r="B2" t="n">
-        <v>75507</v>
+        <v>75512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>92997</v>
+        <v>93003</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>92997</v>
+        <v>93003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137091905</v>
       </c>
       <c r="B7" t="n">
-        <v>90057</v>
+        <v>90062</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091434</v>
       </c>
       <c r="B2" t="n">
-        <v>75512</v>
+        <v>75523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>93003</v>
+        <v>93015</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>93003</v>
+        <v>93015</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137091905</v>
       </c>
       <c r="B7" t="n">
-        <v>90062</v>
+        <v>90073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>93015</v>
+        <v>93016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>93015</v>
+        <v>93016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137091905</v>
       </c>
       <c r="B7" t="n">
-        <v>90073</v>
+        <v>90074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>93016</v>
+        <v>93019</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>93016</v>
+        <v>93019</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137091905</v>
       </c>
       <c r="B7" t="n">
-        <v>90074</v>
+        <v>90077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29015-2026 artfynd.xlsx
+++ b/artfynd/A 29015-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137091434</v>
       </c>
       <c r="B2" t="n">
-        <v>75523</v>
+        <v>75527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137091322</v>
       </c>
       <c r="B4" t="n">
-        <v>93019</v>
+        <v>93023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137091650</v>
       </c>
       <c r="B5" t="n">
-        <v>93019</v>
+        <v>93023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>137091905</v>
       </c>
       <c r="B7" t="n">
-        <v>90077</v>
+        <v>90081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
